--- a/salidas/empresas/PG.xlsx
+++ b/salidas/empresas/PG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>33.62871551513672</v>
+        <v>33.62870407104492</v>
       </c>
       <c r="C3" t="n">
         <v>59.93000030517578</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>32.33811187744141</v>
+        <v>32.33808898925781</v>
       </c>
       <c r="C4" t="n">
         <v>57.63000106811523</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>30.61045074462891</v>
+        <v>30.61043930053711</v>
       </c>
       <c r="C6" t="n">
         <v>54.25</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>31.37217140197754</v>
+        <v>31.37216758728027</v>
       </c>
       <c r="C7" t="n">
         <v>55.59999847412109</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>31.88784599304199</v>
+        <v>31.88784980773926</v>
       </c>
       <c r="C8" t="n">
         <v>56.20000076293945</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.12202453613281</v>
+        <v>35.12200927734375</v>
       </c>
       <c r="C9" t="n">
         <v>61.90000152587891</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>35.16741943359375</v>
+        <v>35.16740036010742</v>
       </c>
       <c r="C10" t="n">
         <v>61.97999954223633</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.1474609375</v>
+        <v>36.14745330810547</v>
       </c>
       <c r="C11" t="n">
         <v>63.38999938964844</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>35.80531311035156</v>
+        <v>35.80531692504883</v>
       </c>
       <c r="C12" t="n">
         <v>62.79000091552734</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>36.64925384521484</v>
+        <v>36.64926147460938</v>
       </c>
       <c r="C13" t="n">
         <v>64.26999664306641</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>37.16867446899414</v>
+        <v>37.16866302490234</v>
       </c>
       <c r="C14" t="n">
         <v>64.87000274658203</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>36.37796020507812</v>
+        <v>36.37797927856445</v>
       </c>
       <c r="C15" t="n">
         <v>63.4900016784668</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.18889999389648</v>
+        <v>36.18889236450195</v>
       </c>
       <c r="C16" t="n">
         <v>63.15999984741211</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>37.10313415527344</v>
+        <v>37.1031608581543</v>
       </c>
       <c r="C17" t="n">
         <v>64.40000152587891</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>35.25374221801758</v>
+        <v>35.25375747680664</v>
       </c>
       <c r="C19" t="n">
         <v>61.18999862670898</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.83989334106445</v>
+        <v>35.83989715576172</v>
       </c>
       <c r="C20" t="n">
         <v>61.86000061035156</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>37.83872222900391</v>
+        <v>37.83871841430664</v>
       </c>
       <c r="C21" t="n">
         <v>65.30999755859375</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.08639907836914</v>
+        <v>43.08638381958008</v>
       </c>
       <c r="C24" t="n">
         <v>74</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>42.74869155883789</v>
+        <v>42.74869537353516</v>
       </c>
       <c r="C25" t="n">
         <v>73.41999816894531</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.28292083740234</v>
+        <v>38.28293609619141</v>
       </c>
       <c r="C26" t="n">
         <v>65.41999816894531</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>38.72766876220703</v>
+        <v>38.72767639160156</v>
       </c>
       <c r="C27" t="n">
         <v>66.18000030517578</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.00405120849609</v>
+        <v>41.00403594970703</v>
       </c>
       <c r="C28" t="n">
         <v>70.06999969482422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>39.46154022216797</v>
+        <v>39.46155548095703</v>
       </c>
       <c r="C29" t="n">
         <v>67.05000305175781</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.87302398681641</v>
+        <v>38.87300872802734</v>
       </c>
       <c r="C30" t="n">
         <v>66.05000305175781</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>35.78906631469727</v>
+        <v>35.78905487060547</v>
       </c>
       <c r="C31" t="n">
         <v>60.81000137329102</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>38.77858352661133</v>
+        <v>38.77859878540039</v>
       </c>
       <c r="C32" t="n">
         <v>65.48000335693359</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.27182006835938</v>
+        <v>41.27184295654297</v>
       </c>
       <c r="C34" t="n">
         <v>69.69000244140625</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.4662971496582</v>
+        <v>38.46628570556641</v>
       </c>
       <c r="C35" t="n">
         <v>64.54000091552734</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>38.35303115844727</v>
+        <v>38.35305023193359</v>
       </c>
       <c r="C36" t="n">
         <v>64.34999847412109</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.84514617919922</v>
+        <v>36.84514236450195</v>
       </c>
       <c r="C37" t="n">
         <v>61.81999969482422</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>32.7101936340332</v>
+        <v>32.71020889282227</v>
       </c>
       <c r="C38" t="n">
         <v>54.5</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.9110107421875</v>
+        <v>28.91102600097656</v>
       </c>
       <c r="C39" t="n">
         <v>48.16999816894531</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>28.2628173828125</v>
+        <v>28.2628116607666</v>
       </c>
       <c r="C40" t="n">
         <v>47.09000015258789</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.92962265014648</v>
+        <v>29.92961692810059</v>
       </c>
       <c r="C41" t="n">
         <v>49.43999862670898</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.44306182861328</v>
+        <v>31.44304466247559</v>
       </c>
       <c r="C42" t="n">
         <v>51.93999862670898</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>30.93453216552734</v>
+        <v>30.93452453613281</v>
       </c>
       <c r="C43" t="n">
         <v>51.09999847412109</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.01853179931641</v>
+        <v>33.01852798461914</v>
       </c>
       <c r="C45" t="n">
         <v>54.11000061035156</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>35.66218185424805</v>
+        <v>35.66217422485352</v>
       </c>
       <c r="C47" t="n">
         <v>58</v>
@@ -1362,11 +1374,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>38.33684158325195</v>
+        <v>38.33683776855469</v>
       </c>
       <c r="C48" t="n">
         <v>62.34999847412109</v>
@@ -1387,11 +1399,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>37.27927780151367</v>
+        <v>37.27926254272461</v>
       </c>
       <c r="C49" t="n">
         <v>60.63000106811523</v>
@@ -1412,11 +1424,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>38.11667251586914</v>
+        <v>38.1166877746582</v>
       </c>
       <c r="C50" t="n">
         <v>61.54999923706055</v>
@@ -1437,11 +1449,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>39.18803787231445</v>
+        <v>39.18803405761719</v>
       </c>
       <c r="C51" t="n">
         <v>63.27999877929688</v>
@@ -1462,11 +1474,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.18183135986328</v>
+        <v>39.18182373046875</v>
       </c>
       <c r="C52" t="n">
         <v>63.27000045776367</v>
@@ -1487,11 +1499,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.79069900512695</v>
+        <v>38.79070281982422</v>
       </c>
       <c r="C53" t="n">
         <v>62.15999984741211</v>
@@ -1512,11 +1524,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>38.12297821044922</v>
+        <v>38.12298202514648</v>
       </c>
       <c r="C54" t="n">
         <v>61.09000015258789</v>
@@ -1537,11 +1549,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.43028259277344</v>
+        <v>37.43027877807617</v>
       </c>
       <c r="C55" t="n">
         <v>59.97999954223633</v>
@@ -1562,11 +1574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.46536254882812</v>
+        <v>38.46535873413086</v>
       </c>
       <c r="C56" t="n">
         <v>61.15999984741211</v>
@@ -1587,11 +1599,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>37.52824020385742</v>
+        <v>37.52825164794922</v>
       </c>
       <c r="C57" t="n">
         <v>59.66999816894531</v>
@@ -1616,11 +1628,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>37.71694183349609</v>
+        <v>37.7169303894043</v>
       </c>
       <c r="C58" t="n">
         <v>59.97000122070312</v>
@@ -1645,11 +1657,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.28844451904297</v>
+        <v>40.28843307495117</v>
       </c>
       <c r="C59" t="n">
         <v>63.56999969482422</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>38.70402526855469</v>
+        <v>38.70401763916016</v>
       </c>
       <c r="C60" t="n">
         <v>61.06999969482422</v>
@@ -1703,7 +1715,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1732,11 +1744,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>40.30617904663086</v>
+        <v>40.30619430541992</v>
       </c>
       <c r="C62" t="n">
         <v>63.13000106811523</v>
@@ -1761,11 +1773,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>40.25510406494141</v>
+        <v>40.2551155090332</v>
       </c>
       <c r="C63" t="n">
         <v>63.04999923706055</v>
@@ -1790,11 +1802,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>39.32934188842773</v>
+        <v>39.3293342590332</v>
       </c>
       <c r="C64" t="n">
         <v>61.59999847412109</v>
@@ -1819,11 +1831,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>41.77990341186523</v>
+        <v>41.77989959716797</v>
       </c>
       <c r="C65" t="n">
         <v>64.90000152587891</v>
@@ -1848,11 +1860,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.13179016113281</v>
+        <v>43.13178634643555</v>
       </c>
       <c r="C66" t="n">
         <v>67</v>
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>40.9237060546875</v>
+        <v>40.92370223999023</v>
       </c>
       <c r="C67" t="n">
         <v>63.56999969482422</v>
@@ -1906,11 +1918,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.90897750854492</v>
+        <v>39.90896987915039</v>
       </c>
       <c r="C68" t="n">
         <v>61.4900016784668</v>
@@ -1935,11 +1947,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>41.33036422729492</v>
+        <v>41.33035659790039</v>
       </c>
       <c r="C69" t="n">
         <v>63.68000030517578</v>
@@ -1964,7 +1976,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1993,11 +2005,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.87014389038086</v>
+        <v>41.87015914916992</v>
       </c>
       <c r="C71" t="n">
         <v>63.9900016784668</v>
@@ -2022,11 +2034,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>42.24966812133789</v>
+        <v>42.24965667724609</v>
       </c>
       <c r="C72" t="n">
         <v>64.56999969482422</v>
@@ -2051,11 +2063,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.64992141723633</v>
+        <v>43.64990234375</v>
       </c>
       <c r="C73" t="n">
         <v>66.70999908447266</v>
@@ -2080,11 +2092,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.57798004150391</v>
+        <v>41.57797622680664</v>
       </c>
       <c r="C74" t="n">
         <v>63.04000091552734</v>
@@ -2109,11 +2121,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>44.59872436523438</v>
+        <v>44.59872055053711</v>
       </c>
       <c r="C75" t="n">
         <v>67.62000274658203</v>
@@ -2138,11 +2150,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>44.32829666137695</v>
+        <v>44.32830047607422</v>
       </c>
       <c r="C76" t="n">
         <v>67.20999908447266</v>
@@ -2167,11 +2179,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>42.32875061035156</v>
+        <v>42.32876968383789</v>
       </c>
       <c r="C77" t="n">
         <v>63.63999938964844</v>
@@ -2196,11 +2208,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>41.43084716796875</v>
+        <v>41.43083953857422</v>
       </c>
       <c r="C78" t="n">
         <v>62.29000091552734</v>
@@ -2225,11 +2237,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>40.73912048339844</v>
+        <v>40.73910140991211</v>
       </c>
       <c r="C79" t="n">
         <v>61.25</v>
@@ -2254,11 +2266,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>43.29975509643555</v>
+        <v>43.29974365234375</v>
       </c>
       <c r="C80" t="n">
         <v>64.54000091552734</v>
@@ -2283,11 +2295,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>45.07763671875</v>
+        <v>45.07762145996094</v>
       </c>
       <c r="C81" t="n">
         <v>67.19000244140625</v>
@@ -2312,11 +2324,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>46.53347396850586</v>
+        <v>46.53348159790039</v>
       </c>
       <c r="C82" t="n">
         <v>69.36000061035156</v>
@@ -2341,7 +2353,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2370,11 +2382,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>47.2335205078125</v>
+        <v>47.23351669311523</v>
       </c>
       <c r="C84" t="n">
         <v>69.83000183105469</v>
@@ -2399,7 +2411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2428,11 +2440,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>51.25093841552734</v>
+        <v>51.25094223022461</v>
       </c>
       <c r="C86" t="n">
         <v>75.16000366210938</v>
@@ -2457,11 +2469,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>51.94649887084961</v>
+        <v>51.94646835327148</v>
       </c>
       <c r="C87" t="n">
         <v>76.18000030517578</v>
@@ -2486,11 +2498,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.54654312133789</v>
+        <v>52.54655075073242</v>
       </c>
       <c r="C88" t="n">
         <v>77.05999755859375</v>
@@ -2515,11 +2527,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.7333984375</v>
+        <v>52.73340225219727</v>
       </c>
       <c r="C89" t="n">
         <v>76.76999664306641</v>
@@ -2544,11 +2556,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>52.72653198242188</v>
+        <v>52.72652053833008</v>
       </c>
       <c r="C90" t="n">
         <v>76.76000213623047</v>
@@ -2573,11 +2585,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>52.88449478149414</v>
+        <v>52.88451385498047</v>
       </c>
       <c r="C91" t="n">
         <v>76.98999786376953</v>
@@ -2602,11 +2614,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.57133102416992</v>
+        <v>55.57132720947266</v>
       </c>
       <c r="C92" t="n">
         <v>80.30000305175781</v>
@@ -2631,11 +2643,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.90348815917969</v>
+        <v>53.90349197387695</v>
       </c>
       <c r="C93" t="n">
         <v>77.88999938964844</v>
@@ -2660,11 +2672,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>52.31179428100586</v>
+        <v>52.3117790222168</v>
       </c>
       <c r="C94" t="n">
         <v>75.58999633789062</v>
@@ -2689,11 +2701,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>56.31965255737305</v>
+        <v>56.31965637207031</v>
       </c>
       <c r="C95" t="n">
         <v>80.75</v>
@@ -2718,11 +2730,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>58.73982238769531</v>
+        <v>58.73982620239258</v>
       </c>
       <c r="C96" t="n">
         <v>84.22000122070312</v>
@@ -2747,11 +2759,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.77995681762695</v>
+        <v>56.77997207641602</v>
       </c>
       <c r="C97" t="n">
         <v>81.41000366210938</v>
@@ -2776,11 +2788,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>53.84341430664062</v>
+        <v>53.84341812133789</v>
       </c>
       <c r="C98" t="n">
         <v>76.62000274658203</v>
@@ -2805,11 +2817,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.2769889831543</v>
+        <v>55.27700042724609</v>
       </c>
       <c r="C99" t="n">
         <v>78.66000366210938</v>
@@ -2834,11 +2846,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.64029693603516</v>
+        <v>56.64030838012695</v>
       </c>
       <c r="C100" t="n">
         <v>80.59999847412109</v>
@@ -2863,11 +2875,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>58.47410202026367</v>
+        <v>58.47409057617188</v>
       </c>
       <c r="C101" t="n">
         <v>82.55000305175781</v>
@@ -2892,11 +2904,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>57.2274169921875</v>
+        <v>57.22739410400391</v>
       </c>
       <c r="C102" t="n">
         <v>80.79000091552734</v>
@@ -2921,11 +2933,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>55.66903686523438</v>
+        <v>55.66904067993164</v>
       </c>
       <c r="C103" t="n">
         <v>78.58999633789062</v>
@@ -2950,11 +2962,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>55.20697784423828</v>
+        <v>55.20697021484375</v>
       </c>
       <c r="C104" t="n">
         <v>77.31999969482422</v>
@@ -2979,11 +2991,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>59.34106063842773</v>
+        <v>59.34105682373047</v>
       </c>
       <c r="C105" t="n">
         <v>83.11000061035156</v>
@@ -3008,11 +3020,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>59.7908935546875</v>
+        <v>59.79086685180664</v>
       </c>
       <c r="C106" t="n">
         <v>83.73999786376953</v>
@@ -3037,11 +3049,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>62.78923797607422</v>
+        <v>62.78924179077148</v>
       </c>
       <c r="C107" t="n">
         <v>87.26999664306641</v>
@@ -3066,11 +3078,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.06278228759766</v>
+        <v>65.06279754638672</v>
       </c>
       <c r="C108" t="n">
         <v>90.43000030517578</v>
@@ -3095,11 +3107,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.53765869140625</v>
+        <v>65.53765106201172</v>
       </c>
       <c r="C109" t="n">
         <v>91.08999633789062</v>
@@ -3124,7 +3136,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3153,11 +3165,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>61.68517684936523</v>
+        <v>61.6851921081543</v>
       </c>
       <c r="C111" t="n">
         <v>85.12999725341797</v>
@@ -3182,11 +3194,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>59.37371444702148</v>
+        <v>59.37370681762695</v>
       </c>
       <c r="C112" t="n">
         <v>81.94000244140625</v>
@@ -3211,11 +3223,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>58.07635116577148</v>
+        <v>58.07633209228516</v>
       </c>
       <c r="C113" t="n">
         <v>79.51000213623047</v>
@@ -3240,11 +3252,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>57.25824737548828</v>
+        <v>57.25827407836914</v>
       </c>
       <c r="C114" t="n">
         <v>78.38999938964844</v>
@@ -3269,11 +3281,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>57.1486930847168</v>
+        <v>57.14869689941406</v>
       </c>
       <c r="C115" t="n">
         <v>78.23999786376953</v>
@@ -3298,11 +3310,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>56.48258590698242</v>
+        <v>56.48258972167969</v>
       </c>
       <c r="C116" t="n">
         <v>76.69999694824219</v>
@@ -3327,11 +3339,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>52.04205703735352</v>
+        <v>52.04204559326172</v>
       </c>
       <c r="C117" t="n">
         <v>70.66999816894531</v>
@@ -3356,11 +3368,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>52.97728729248047</v>
+        <v>52.97727584838867</v>
       </c>
       <c r="C118" t="n">
         <v>71.94000244140625</v>
@@ -3385,11 +3397,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.75246810913086</v>
+        <v>56.75244903564453</v>
       </c>
       <c r="C119" t="n">
         <v>76.37999725341797</v>
@@ -3414,11 +3426,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>55.60820007324219</v>
+        <v>55.60819625854492</v>
       </c>
       <c r="C120" t="n">
         <v>74.83999633789062</v>
@@ -3443,11 +3455,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>59.00384902954102</v>
+        <v>59.00384140014648</v>
       </c>
       <c r="C121" t="n">
         <v>79.41000366210938</v>
@@ -3472,11 +3484,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>61.22699356079102</v>
+        <v>61.22701644897461</v>
       </c>
       <c r="C122" t="n">
         <v>81.69000244140625</v>
@@ -3501,11 +3513,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.17771148681641</v>
+        <v>60.17765808105469</v>
       </c>
       <c r="C123" t="n">
         <v>80.29000091552734</v>
@@ -3530,7 +3542,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3559,11 +3571,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.54218673706055</v>
+        <v>60.54217910766602</v>
       </c>
       <c r="C125" t="n">
         <v>80.12000274658203</v>
@@ -3588,7 +3600,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3617,11 +3629,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>63.98037338256836</v>
+        <v>63.9803466796875</v>
       </c>
       <c r="C127" t="n">
         <v>84.66999816894531</v>
@@ -3646,11 +3658,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>65.182373046875</v>
+        <v>65.18236541748047</v>
       </c>
       <c r="C128" t="n">
         <v>85.58999633789062</v>
@@ -3675,11 +3687,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>66.49224090576172</v>
+        <v>66.49225616455078</v>
       </c>
       <c r="C129" t="n">
         <v>87.30999755859375</v>
@@ -3704,11 +3716,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>68.35045623779297</v>
+        <v>68.35047149658203</v>
       </c>
       <c r="C130" t="n">
         <v>89.75</v>
@@ -3733,11 +3745,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>66.61425018310547</v>
+        <v>66.61420440673828</v>
       </c>
       <c r="C131" t="n">
         <v>86.80000305175781</v>
@@ -3762,11 +3774,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.28350067138672</v>
+        <v>63.28351211547852</v>
       </c>
       <c r="C132" t="n">
         <v>82.45999908447266</v>
@@ -3791,11 +3803,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>64.52676391601562</v>
+        <v>64.52677917480469</v>
       </c>
       <c r="C133" t="n">
         <v>84.08000183105469</v>
@@ -3820,11 +3832,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.760986328125</v>
+        <v>67.76095581054688</v>
       </c>
       <c r="C134" t="n">
         <v>87.59999847412109</v>
@@ -3849,11 +3861,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.44514465332031</v>
+        <v>70.44512939453125</v>
       </c>
       <c r="C135" t="n">
         <v>91.06999969482422</v>
@@ -3878,11 +3890,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>69.50141906738281</v>
+        <v>69.50144195556641</v>
       </c>
       <c r="C136" t="n">
         <v>89.84999847412109</v>
@@ -3907,11 +3919,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.06938934326172</v>
+        <v>68.06940460205078</v>
       </c>
       <c r="C137" t="n">
         <v>87.33000183105469</v>
@@ -3936,7 +3948,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3965,11 +3977,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>67.92908477783203</v>
+        <v>67.92910766601562</v>
       </c>
       <c r="C139" t="n">
         <v>87.15000152587891</v>
@@ -3994,11 +4006,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>71.34503936767578</v>
+        <v>71.34505462646484</v>
       </c>
       <c r="C140" t="n">
         <v>90.81999969482422</v>
@@ -4023,11 +4035,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>72.48410797119141</v>
+        <v>72.48411560058594</v>
       </c>
       <c r="C141" t="n">
         <v>92.26999664306641</v>
@@ -4052,11 +4064,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>71.47075653076172</v>
+        <v>71.47074890136719</v>
       </c>
       <c r="C142" t="n">
         <v>90.98000335693359</v>
@@ -4081,11 +4093,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>68.333984375</v>
+        <v>68.33396148681641</v>
       </c>
       <c r="C143" t="n">
         <v>86.33999633789062</v>
@@ -4110,11 +4122,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>71.22275543212891</v>
+        <v>71.22277069091797</v>
       </c>
       <c r="C144" t="n">
         <v>89.98999786376953</v>
@@ -4139,11 +4151,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>72.71860504150391</v>
+        <v>72.71862030029297</v>
       </c>
       <c r="C145" t="n">
         <v>91.87999725341797</v>
@@ -4168,11 +4180,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>68.85492706298828</v>
+        <v>68.85491943359375</v>
       </c>
       <c r="C146" t="n">
         <v>86.33999633789062</v>
@@ -4197,11 +4209,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>62.61859512329102</v>
+        <v>62.61856842041016</v>
       </c>
       <c r="C147" t="n">
         <v>78.51999664306641</v>
@@ -4226,11 +4238,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>63.22467803955078</v>
+        <v>63.22466278076172</v>
       </c>
       <c r="C148" t="n">
         <v>79.27999877929688</v>
@@ -4255,11 +4267,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>58.22395706176758</v>
+        <v>58.22395324707031</v>
       </c>
       <c r="C149" t="n">
         <v>72.33999633789062</v>
@@ -4284,11 +4296,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>58.89199829101562</v>
+        <v>58.89199447631836</v>
       </c>
       <c r="C150" t="n">
         <v>73.16999816894531</v>
@@ -4313,11 +4325,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>62.82778167724609</v>
+        <v>62.82777404785156</v>
       </c>
       <c r="C151" t="n">
         <v>78.05999755859375</v>
@@ -4342,7 +4354,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4371,11 +4383,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>67.36949157714844</v>
+        <v>67.3695068359375</v>
       </c>
       <c r="C153" t="n">
         <v>82.94999694824219</v>
@@ -4400,11 +4412,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>67.59689331054688</v>
+        <v>67.596923828125</v>
       </c>
       <c r="C154" t="n">
         <v>83.23000335693359</v>
@@ -4429,11 +4441,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>72.65965270996094</v>
+        <v>72.65962982177734</v>
       </c>
       <c r="C155" t="n">
         <v>88.68000030517578</v>
@@ -4458,11 +4470,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>77.43643951416016</v>
+        <v>77.43644714355469</v>
       </c>
       <c r="C156" t="n">
         <v>94.51000213623047</v>
@@ -4487,11 +4499,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>75.3143310546875</v>
+        <v>75.31432342529297</v>
       </c>
       <c r="C157" t="n">
         <v>91.91999816894531</v>
@@ -4516,11 +4528,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>79.66751861572266</v>
+        <v>79.66751098632812</v>
       </c>
       <c r="C158" t="n">
         <v>96.47000122070312</v>
@@ -4545,11 +4557,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>81.38523101806641</v>
+        <v>81.38523864746094</v>
       </c>
       <c r="C159" t="n">
         <v>98.55000305175781</v>
@@ -4574,11 +4586,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>85.92729187011719</v>
+        <v>85.92730712890625</v>
       </c>
       <c r="C160" t="n">
         <v>104.0500030517578</v>
@@ -4603,7 +4615,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4632,11 +4644,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>85.58582305908203</v>
+        <v>85.58579254150391</v>
       </c>
       <c r="C162" t="n">
         <v>102.9100036621094</v>
@@ -4661,11 +4673,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>91.19115447998047</v>
+        <v>91.19117736816406</v>
       </c>
       <c r="C163" t="n">
         <v>109.6500015258789</v>
@@ -4690,11 +4702,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>98.80451965332031</v>
+        <v>98.80452728271484</v>
       </c>
       <c r="C164" t="n">
         <v>118.0400009155273</v>
@@ -4719,11 +4731,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>100.6376647949219</v>
+        <v>100.6376190185547</v>
       </c>
       <c r="C165" t="n">
         <v>120.2300033569336</v>
@@ -4748,11 +4760,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>104.1113662719727</v>
+        <v>104.1113586425781</v>
       </c>
       <c r="C166" t="n">
         <v>124.379997253418</v>
@@ -4777,7 +4789,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4806,7 +4818,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4835,11 +4847,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>105.2144546508789</v>
+        <v>105.2144317626953</v>
       </c>
       <c r="C169" t="n">
         <v>124.9000015258789</v>
@@ -4864,11 +4876,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>105.602294921875</v>
+        <v>105.6022796630859</v>
       </c>
       <c r="C170" t="n">
         <v>124.620002746582</v>
@@ -4893,11 +4905,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>95.95046997070312</v>
+        <v>95.95047760009766</v>
       </c>
       <c r="C171" t="n">
         <v>113.2300033569336</v>
@@ -4922,11 +4934,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>93.21338653564453</v>
+        <v>93.21337890625</v>
       </c>
       <c r="C172" t="n">
         <v>110</v>
@@ -4951,7 +4963,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4980,11 +4992,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>98.88505554199219</v>
+        <v>98.88504791259766</v>
       </c>
       <c r="C174" t="n">
         <v>115.9199981689453</v>
@@ -5009,11 +5021,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>101.9986724853516</v>
+        <v>101.998664855957</v>
       </c>
       <c r="C175" t="n">
         <v>119.5699996948242</v>
@@ -5038,11 +5050,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>112.5571517944336</v>
+        <v>112.5571594238281</v>
       </c>
       <c r="C176" t="n">
         <v>131.1199951171875</v>
@@ -5067,11 +5079,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>118.746452331543</v>
+        <v>118.7464218139648</v>
       </c>
       <c r="C177" t="n">
         <v>138.3300018310547</v>
@@ -5096,11 +5108,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>119.3130035400391</v>
+        <v>119.31298828125</v>
       </c>
       <c r="C178" t="n">
         <v>138.9900054931641</v>
@@ -5125,11 +5137,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>118.3440399169922</v>
+        <v>118.3440475463867</v>
       </c>
       <c r="C179" t="n">
         <v>137.1000061035156</v>
@@ -5154,11 +5166,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>119.8719100952148</v>
+        <v>119.8719024658203</v>
       </c>
       <c r="C180" t="n">
         <v>138.8699951171875</v>
@@ -5183,11 +5195,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>120.1049728393555</v>
+        <v>120.1049499511719</v>
       </c>
       <c r="C181" t="n">
         <v>139.1399993896484</v>
@@ -5212,11 +5224,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>111.3377914428711</v>
+        <v>111.3377838134766</v>
       </c>
       <c r="C182" t="n">
         <v>128.2100067138672</v>
@@ -5241,11 +5253,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>107.2736663818359</v>
+        <v>107.273681640625</v>
       </c>
       <c r="C183" t="n">
         <v>123.5299987792969</v>
@@ -5270,11 +5282,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>117.6076431274414</v>
+        <v>117.6076583862305</v>
       </c>
       <c r="C184" t="n">
         <v>135.4299926757812</v>
@@ -5299,11 +5311,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>116.6034545898438</v>
+        <v>116.6034469604492</v>
       </c>
       <c r="C185" t="n">
         <v>133.4199981689453</v>
@@ -5328,11 +5340,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>117.8532104492188</v>
+        <v>117.8532180786133</v>
       </c>
       <c r="C186" t="n">
         <v>134.8500061035156</v>
@@ -5357,11 +5369,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>117.9231338500977</v>
+        <v>117.9231262207031</v>
       </c>
       <c r="C187" t="n">
         <v>134.9299926757812</v>
@@ -5386,11 +5398,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>125.0847778320312</v>
+        <v>125.0847702026367</v>
       </c>
       <c r="C188" t="n">
         <v>142.2299957275391</v>
@@ -5415,7 +5427,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5444,11 +5456,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>122.9477233886719</v>
+        <v>122.9477310180664</v>
       </c>
       <c r="C190" t="n">
         <v>139.8000030517578</v>
@@ -5473,11 +5485,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>126.5327377319336</v>
+        <v>126.5327529907227</v>
       </c>
       <c r="C191" t="n">
         <v>142.9900054931641</v>
@@ -5502,11 +5514,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>127.9397506713867</v>
+        <v>127.9397430419922</v>
       </c>
       <c r="C192" t="n">
         <v>144.5800018310547</v>
@@ -5531,11 +5543,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>144.7529907226562</v>
+        <v>144.7529602050781</v>
       </c>
       <c r="C193" t="n">
         <v>163.5800018310547</v>
@@ -5560,11 +5572,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>142.7498931884766</v>
+        <v>142.7498168945312</v>
       </c>
       <c r="C194" t="n">
         <v>160.4499969482422</v>
@@ -5589,11 +5601,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>138.6928558349609</v>
+        <v>138.6929168701172</v>
       </c>
       <c r="C195" t="n">
         <v>155.8899993896484</v>
@@ -5618,7 +5630,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5647,11 +5659,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>143.6401824951172</v>
+        <v>143.6401519775391</v>
       </c>
       <c r="C197" t="n">
         <v>160.5500030517578</v>
@@ -5676,11 +5688,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>132.3046417236328</v>
+        <v>132.3046264648438</v>
       </c>
       <c r="C198" t="n">
         <v>147.8800048828125</v>
@@ -5705,11 +5717,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>128.6454162597656</v>
+        <v>128.6454315185547</v>
       </c>
       <c r="C199" t="n">
         <v>143.7899932861328</v>
@@ -5734,11 +5746,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>125.0861968994141</v>
+        <v>125.0862045288086</v>
       </c>
       <c r="C200" t="n">
         <v>138.9100036621094</v>
@@ -5763,11 +5775,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>124.2127304077148</v>
+        <v>124.2127227783203</v>
       </c>
       <c r="C201" t="n">
         <v>137.9400024414062</v>
@@ -5792,11 +5804,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>113.6860580444336</v>
+        <v>113.6860733032227</v>
       </c>
       <c r="C202" t="n">
         <v>126.25</v>
@@ -5821,11 +5833,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>122.1287841796875</v>
+        <v>122.128776550293</v>
       </c>
       <c r="C203" t="n">
         <v>134.6699981689453</v>
@@ -5850,7 +5862,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5879,11 +5891,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>137.4458923339844</v>
+        <v>137.4459075927734</v>
       </c>
       <c r="C205" t="n">
         <v>151.5599975585938</v>
@@ -5908,7 +5920,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5937,11 +5949,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>125.5324478149414</v>
+        <v>125.532470703125</v>
       </c>
       <c r="C207" t="n">
         <v>137.5599975585938</v>
@@ -5966,11 +5978,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>135.6893005371094</v>
+        <v>135.6892852783203</v>
       </c>
       <c r="C208" t="n">
         <v>148.6900024414062</v>
@@ -5995,11 +6007,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>143.6004028320312</v>
+        <v>143.6004180908203</v>
       </c>
       <c r="C209" t="n">
         <v>156.3800048828125</v>
@@ -6024,11 +6036,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>130.8546600341797</v>
+        <v>130.8546905517578</v>
       </c>
       <c r="C210" t="n">
         <v>142.5</v>
@@ -6053,11 +6065,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>139.3396148681641</v>
+        <v>139.339599609375</v>
       </c>
       <c r="C211" t="n">
         <v>151.7400054931641</v>
@@ -6082,11 +6094,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>144.4312591552734</v>
+        <v>144.4312438964844</v>
       </c>
       <c r="C212" t="n">
         <v>156.3000030517578</v>
@@ -6111,11 +6123,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.6200714111328</v>
+        <v>142.6200866699219</v>
       </c>
       <c r="C213" t="n">
         <v>154.3399963378906</v>
@@ -6140,7 +6152,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6169,7 +6181,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6198,7 +6210,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6227,11 +6239,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>136.2670593261719</v>
+        <v>136.2670440673828</v>
       </c>
       <c r="C217" t="n">
         <v>146.5399932861328</v>
@@ -6256,11 +6268,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>147.0467834472656</v>
+        <v>147.0468139648438</v>
       </c>
       <c r="C218" t="n">
         <v>157.1399993896484</v>
@@ -6285,11 +6297,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>148.7311859130859</v>
+        <v>148.731201171875</v>
       </c>
       <c r="C219" t="n">
         <v>158.9400024414062</v>
@@ -6314,7 +6326,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6343,11 +6355,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>153.7036743164062</v>
+        <v>153.7037048339844</v>
       </c>
       <c r="C221" t="n">
         <v>163.1999969482422</v>
@@ -6372,7 +6384,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6401,11 +6413,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>155.3235931396484</v>
+        <v>155.3235778808594</v>
       </c>
       <c r="C223" t="n">
         <v>164.9199981689453</v>
@@ -6430,11 +6442,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>152.3162536621094</v>
+        <v>152.3162384033203</v>
       </c>
       <c r="C224" t="n">
         <v>160.7599945068359</v>
@@ -6459,7 +6471,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6488,11 +6500,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>164.1028594970703</v>
+        <v>164.1028900146484</v>
       </c>
       <c r="C226" t="n">
         <v>173.1999969482422</v>
@@ -6517,7 +6529,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6546,11 +6558,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>170.8431701660156</v>
+        <v>170.8431854248047</v>
       </c>
       <c r="C228" t="n">
         <v>179.2599945068359</v>
@@ -6575,11 +6587,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>159.7782897949219</v>
+        <v>159.7783050537109</v>
       </c>
       <c r="C229" t="n">
         <v>167.6499938964844</v>
@@ -6604,11 +6616,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>159.160888671875</v>
+        <v>159.1609191894531</v>
       </c>
       <c r="C230" t="n">
         <v>165.9900054931641</v>
@@ -6633,11 +6645,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>166.6879272460938</v>
+        <v>166.6879119873047</v>
       </c>
       <c r="C231" t="n">
         <v>173.8399963378906</v>
@@ -6662,11 +6674,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>163.4086151123047</v>
+        <v>163.4086303710938</v>
       </c>
       <c r="C232" t="n">
         <v>170.4199981689453</v>
@@ -6691,11 +6703,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>156.853271484375</v>
+        <v>156.8532562255859</v>
       </c>
       <c r="C233" t="n">
         <v>162.5700073242188</v>
@@ -6720,11 +6732,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>163.9158325195312</v>
+        <v>163.9158630371094</v>
       </c>
       <c r="C234" t="n">
         <v>169.8899993896484</v>
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6778,11 +6790,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>146.1715850830078</v>
+        <v>146.1715698242188</v>
       </c>
       <c r="C236" t="n">
         <v>150.4700012207031</v>
@@ -6807,7 +6819,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6836,7 +6848,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6865,7 +6877,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6894,7 +6906,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6923,7 +6935,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6952,7 +6964,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6981,7 +6993,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7010,7 +7022,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7039,7 +7051,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7068,7 +7080,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7097,7 +7109,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7126,7 +7138,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7155,7 +7167,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7184,32 +7196,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>147.3899993896484</v>
+        <v>145.6799926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>147.3899993896484</v>
+        <v>145.6799926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>129853300</v>
+        <v>137281700</v>
       </c>
       <c r="E250" t="n">
         <v>6.620000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>22.26435036097408</v>
+        <v>22.00604118969505</v>
       </c>
       <c r="G250" t="n">
         <v>2324433060</v>
       </c>
       <c r="H250" t="n">
-        <v>342598187294.6786</v>
+        <v>338623391156.1438</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05586450400942069</v>
+        <v>0.05906029404004433</v>
       </c>
     </row>
   </sheetData>
@@ -7241,75 +7253,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7462,7 +7474,7 @@
       <c r="I5" t="n">
         <v>4.25</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="K5" t="n">
@@ -7475,13 +7487,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7508,7 +7520,7 @@
       <c r="I6" t="n">
         <v>4.279999999999999</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="K6" t="n">
@@ -7521,13 +7533,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7554,7 +7566,7 @@
       <c r="I7" t="n">
         <v>4.19</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="K7" t="n">
@@ -7567,13 +7579,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7600,7 +7612,7 @@
       <c r="I8" t="n">
         <v>4.18</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="K8" t="n">
@@ -7613,13 +7625,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7646,7 +7658,7 @@
       <c r="I9" t="n">
         <v>4.09</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="K9" t="n">
@@ -7659,13 +7671,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7692,7 +7704,7 @@
       <c r="I10" t="n">
         <v>4.05</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="K10" t="n">
@@ -7705,13 +7717,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7738,7 +7750,7 @@
       <c r="I11" t="n">
         <v>3.67</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K11" t="n">
@@ -7751,13 +7763,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7784,7 +7796,7 @@
       <c r="I12" t="n">
         <v>3.8</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="K12" t="n">
@@ -7797,13 +7809,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40765</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7830,7 +7842,7 @@
       <c r="I13" t="n">
         <v>3.93</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40765</v>
       </c>
       <c r="K13" t="n">
@@ -7843,13 +7855,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7876,7 +7888,7 @@
       <c r="I14" t="n">
         <v>3.94</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K14" t="n">
@@ -7889,13 +7901,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7922,7 +7934,7 @@
       <c r="I15" t="n">
         <v>3.4</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="K15" t="n">
@@ -7935,13 +7947,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7968,7 +7980,7 @@
       <c r="I16" t="n">
         <v>3.26</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K16" t="n">
@@ -7981,13 +7993,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8014,7 +8026,7 @@
       <c r="I17" t="n">
         <v>3.66</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -8027,13 +8039,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8060,7 +8072,7 @@
       <c r="I18" t="n">
         <v>3.59</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K18" t="n">
@@ -8073,13 +8085,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8106,7 +8118,7 @@
       <c r="I19" t="n">
         <v>4.41</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="K19" t="n">
@@ -8119,13 +8131,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8152,7 +8164,7 @@
       <c r="I20" t="n">
         <v>4.47</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K20" t="n">
@@ -8165,13 +8177,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8198,7 +8210,7 @@
       <c r="I21" t="n">
         <v>3.87</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K21" t="n">
@@ -8211,13 +8223,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8244,7 +8256,7 @@
       <c r="I22" t="n">
         <v>3.945119515781554</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="K22" t="n">
@@ -8257,13 +8269,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8290,7 +8302,7 @@
       <c r="I23" t="n">
         <v>3.733733921832784</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="K23" t="n">
@@ -8303,13 +8315,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8336,7 +8348,7 @@
       <c r="I24" t="n">
         <v>3.753733921832783</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K24" t="n">
@@ -8349,13 +8361,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8382,7 +8394,7 @@
       <c r="I25" t="n">
         <v>4.003733921832783</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K25" t="n">
@@ -8395,13 +8407,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8428,7 +8440,7 @@
       <c r="I26" t="n">
         <v>3.658614406051229</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K26" t="n">
@@ -8441,13 +8453,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8474,7 +8486,7 @@
       <c r="I27" t="n">
         <v>3.3</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="K27" t="n">
@@ -8487,13 +8499,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8520,7 +8532,7 @@
       <c r="I28" t="n">
         <v>3.15</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K28" t="n">
@@ -8533,13 +8545,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8566,7 +8578,7 @@
       <c r="I29" t="n">
         <v>2.44</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K29" t="n">
@@ -8579,13 +8591,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8612,7 +8624,7 @@
       <c r="I30" t="n">
         <v>2.66</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K30" t="n">
@@ -8625,13 +8637,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8658,7 +8670,7 @@
       <c r="I31" t="n">
         <v>2.96</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="K31" t="n">
@@ -8671,13 +8683,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8704,7 +8716,7 @@
       <c r="I32" t="n">
         <v>3.18</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K32" t="n">
@@ -8717,13 +8729,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8750,7 +8762,7 @@
       <c r="I33" t="n">
         <v>3.69</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="K33" t="n">
@@ -8763,13 +8775,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8796,7 +8808,7 @@
       <c r="I34" t="n">
         <v>3.74</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K34" t="n">
@@ -8809,13 +8821,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8842,7 +8854,7 @@
       <c r="I35" t="n">
         <v>5.5</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="K35" t="n">
@@ -8855,13 +8867,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8888,7 +8900,7 @@
       <c r="I36" t="n">
         <v>5.459999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K36" t="n">
@@ -8901,13 +8913,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8934,7 +8946,7 @@
       <c r="I37" t="n">
         <v>5.59</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="K37" t="n">
@@ -8947,13 +8959,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8980,7 +8992,7 @@
       <c r="I38" t="n">
         <v>5.69</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="K38" t="n">
@@ -8993,13 +9005,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43123</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9026,7 +9038,7 @@
       <c r="I39" t="n">
         <v>3.74</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43123</v>
       </c>
       <c r="K39" t="n">
@@ -9039,13 +9051,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9072,7 +9084,7 @@
       <c r="I40" t="n">
         <v>3.76</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="K40" t="n">
@@ -9085,13 +9097,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9118,7 +9130,7 @@
       <c r="I41" t="n">
         <v>3.66</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="K41" t="n">
@@ -9131,13 +9143,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9164,7 +9176,7 @@
       <c r="I42" t="n">
         <v>3.82</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="K42" t="n">
@@ -9177,13 +9189,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9210,7 +9222,7 @@
       <c r="I43" t="n">
         <v>4.109999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="K43" t="n">
@@ -9223,13 +9235,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9256,7 +9268,7 @@
       <c r="I44" t="n">
         <v>4.2</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="K44" t="n">
@@ -9269,13 +9281,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9302,7 +9314,7 @@
       <c r="I45" t="n">
         <v>1.36</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K45" t="n">
@@ -9315,13 +9327,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9348,7 +9360,7 @@
       <c r="I46" t="n">
         <v>1.5</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="K46" t="n">
@@ -9361,13 +9373,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43853</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9394,7 +9406,7 @@
       <c r="I47" t="n">
         <v>1.69</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43853</v>
       </c>
       <c r="K47" t="n">
@@ -9407,13 +9419,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43941</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9440,7 +9452,7 @@
       <c r="I48" t="n">
         <v>1.77</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43941</v>
       </c>
       <c r="K48" t="n">
@@ -9453,13 +9465,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9486,7 +9498,7 @@
       <c r="I49" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9499,13 +9511,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9532,7 +9544,7 @@
       <c r="I50" t="n">
         <v>5.23</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="K50" t="n">
@@ -9545,13 +9557,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44216</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9578,7 +9590,7 @@
       <c r="I51" t="n">
         <v>5.290000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44216</v>
       </c>
       <c r="K51" t="n">
@@ -9591,13 +9603,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9624,7 +9636,7 @@
       <c r="I52" t="n">
         <v>5.430000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="K52" t="n">
@@ -9637,13 +9649,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9670,7 +9682,7 @@
       <c r="I53" t="n">
         <v>5.500000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K53" t="n">
@@ -9683,13 +9695,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9716,7 +9728,7 @@
       <c r="I54" t="n">
         <v>5.48</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="K54" t="n">
@@ -9729,13 +9741,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44580</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9762,7 +9774,7 @@
       <c r="I55" t="n">
         <v>5.670000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44580</v>
       </c>
       <c r="K55" t="n">
@@ -9775,13 +9787,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44671</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9808,7 +9820,7 @@
       <c r="I56" t="n">
         <v>5.740000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44671</v>
       </c>
       <c r="K56" t="n">
@@ -9821,13 +9833,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9854,7 +9866,7 @@
       <c r="I57" t="n">
         <v>5.81</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K57" t="n">
@@ -9867,13 +9879,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9900,7 +9912,7 @@
       <c r="I58" t="n">
         <v>5.77</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="K58" t="n">
@@ -9913,13 +9925,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44945</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9946,7 +9958,7 @@
       <c r="I59" t="n">
         <v>5.7</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44945</v>
       </c>
       <c r="K59" t="n">
@@ -9959,13 +9971,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9992,7 +10004,7 @@
       <c r="I60" t="n">
         <v>5.74</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="K60" t="n">
@@ -10005,13 +10017,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10038,7 +10050,7 @@
       <c r="I61" t="n">
         <v>5.9</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10051,13 +10063,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10084,7 +10096,7 @@
       <c r="I62" t="n">
         <v>6.16</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="K62" t="n">
@@ -10097,13 +10109,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45314</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10130,7 +10142,7 @@
       <c r="I63" t="n">
         <v>5.970000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45314</v>
       </c>
       <c r="K63" t="n">
@@ -10143,13 +10155,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10176,7 +10188,7 @@
       <c r="I64" t="n">
         <v>6.12</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="K64" t="n">
@@ -10189,13 +10201,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10222,7 +10234,7 @@
       <c r="I65" t="n">
         <v>6.02</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K65" t="n">
@@ -10235,13 +10247,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10268,7 +10280,7 @@
       <c r="I66" t="n">
         <v>5.8</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="K66" t="n">
@@ -10281,13 +10293,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10314,7 +10326,7 @@
       <c r="I67" t="n">
         <v>6.28</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="K67" t="n">
@@ -10327,13 +10339,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10360,7 +10372,7 @@
       <c r="I68" t="n">
         <v>6.3</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -10373,13 +10385,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10406,7 +10418,7 @@
       <c r="I69" t="n">
         <v>6.51</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="K69" t="n">
@@ -10419,13 +10431,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10452,7 +10464,7 @@
       <c r="I70" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K70" t="n">
@@ -10465,13 +10477,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10498,7 +10510,7 @@
       <c r="I71" t="n">
         <v>6.75</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="K71" t="n">
@@ -10511,13 +10523,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10544,7 +10556,7 @@
       <c r="I72" t="n">
         <v>6.84</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K72" t="n">
@@ -10557,13 +10569,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10590,7 +10602,7 @@
       <c r="I73" t="n">
         <v>6.620000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K73" t="n">
@@ -10627,52 +10639,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C2" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="C3" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="C4" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40403</v>
       </c>
       <c r="C5" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C6" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="C7" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C8" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40765</v>
       </c>
       <c r="C9" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C10" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="C11" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C12" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C13" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C14" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="C15" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C16" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C17" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="C18" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="C19" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C20" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C21" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C22" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="C23" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C24" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C25" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C26" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="C27" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C28" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="C29" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C30" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="C31" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C32" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="C33" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="C34" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43123</v>
       </c>
       <c r="C35" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43209</v>
       </c>
       <c r="C36" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="C37" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="C38" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="C39" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="C40" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C41" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="C42" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43853</v>
       </c>
       <c r="C43" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43941</v>
       </c>
       <c r="C44" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C45" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="C46" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44216</v>
       </c>
       <c r="C47" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="C48" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C49" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="C50" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44580</v>
       </c>
       <c r="C51" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44671</v>
       </c>
       <c r="C52" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C53" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="C54" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44945</v>
       </c>
       <c r="C55" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="C56" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C57" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="C58" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45314</v>
       </c>
       <c r="C59" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="C60" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C61" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="C62" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="C63" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C64" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="C65" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C66" t="n">
@@ -12749,10 +12761,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="C67" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C68" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C69" t="n">
@@ -12863,12 +12875,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PG.xlsx
+++ b/salidas/empresas/PG.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.23591613769531</v>
+        <v>33.23590469360352</v>
       </c>
       <c r="C2" t="n">
         <v>59.22999954223633</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>33.62870407104492</v>
+        <v>33.62869644165039</v>
       </c>
       <c r="C3" t="n">
         <v>59.93000030517578</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>32.33808898925781</v>
+        <v>32.33809661865234</v>
       </c>
       <c r="C4" t="n">
         <v>57.63000106811523</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.8448486328125</v>
+        <v>32.84485626220703</v>
       </c>
       <c r="C5" t="n">
         <v>58.20999908447266</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>31.37216758728027</v>
+        <v>31.37217712402344</v>
       </c>
       <c r="C7" t="n">
         <v>55.59999847412109</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>31.88784980773926</v>
+        <v>31.88784027099609</v>
       </c>
       <c r="C8" t="n">
         <v>56.20000076293945</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.12200927734375</v>
+        <v>35.12200164794922</v>
       </c>
       <c r="C9" t="n">
         <v>61.90000152587891</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>35.16740036010742</v>
+        <v>35.16740798950195</v>
       </c>
       <c r="C10" t="n">
         <v>61.97999954223633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.14745330810547</v>
+        <v>36.14745712280273</v>
       </c>
       <c r="C11" t="n">
         <v>63.38999938964844</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>36.64926147460938</v>
+        <v>36.64926910400391</v>
       </c>
       <c r="C13" t="n">
         <v>64.26999664306641</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>37.16866302490234</v>
+        <v>37.16868209838867</v>
       </c>
       <c r="C14" t="n">
         <v>64.87000274658203</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>36.37797927856445</v>
+        <v>36.37797546386719</v>
       </c>
       <c r="C15" t="n">
         <v>63.4900016784668</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.18889236450195</v>
+        <v>36.18889617919922</v>
       </c>
       <c r="C16" t="n">
         <v>63.15999984741211</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>37.1031608581543</v>
+        <v>37.10315322875977</v>
       </c>
       <c r="C17" t="n">
         <v>64.40000152587891</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>36.61343383789062</v>
+        <v>36.61344146728516</v>
       </c>
       <c r="C18" t="n">
         <v>63.54999923706055</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>35.25375747680664</v>
+        <v>35.25374603271484</v>
       </c>
       <c r="C19" t="n">
         <v>61.18999862670898</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.83989715576172</v>
+        <v>35.83988571166992</v>
       </c>
       <c r="C20" t="n">
         <v>61.86000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>40.75294494628906</v>
+        <v>40.75296020507812</v>
       </c>
       <c r="C22" t="n">
         <v>70.33999633789062</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>40.47792053222656</v>
+        <v>40.47792434692383</v>
       </c>
       <c r="C23" t="n">
         <v>69.51999664306641</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.08638381958008</v>
+        <v>43.08637237548828</v>
       </c>
       <c r="C24" t="n">
         <v>74</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>42.74869537353516</v>
+        <v>42.74868774414062</v>
       </c>
       <c r="C25" t="n">
         <v>73.41999816894531</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.28293609619141</v>
+        <v>38.28295135498047</v>
       </c>
       <c r="C26" t="n">
         <v>65.41999816894531</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.00403594970703</v>
+        <v>41.00404739379883</v>
       </c>
       <c r="C28" t="n">
         <v>70.06999969482422</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.87300872802734</v>
+        <v>38.87300491333008</v>
       </c>
       <c r="C30" t="n">
         <v>66.05000305175781</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>38.77859878540039</v>
+        <v>38.77857971191406</v>
       </c>
       <c r="C32" t="n">
         <v>65.48000335693359</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>41.3192138671875</v>
+        <v>41.31922149658203</v>
       </c>
       <c r="C33" t="n">
         <v>69.76999664306641</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.27184295654297</v>
+        <v>41.2718505859375</v>
       </c>
       <c r="C34" t="n">
         <v>69.69000244140625</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.46628570556641</v>
+        <v>38.46628189086914</v>
       </c>
       <c r="C35" t="n">
         <v>64.54000091552734</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>38.35305023193359</v>
+        <v>38.35304641723633</v>
       </c>
       <c r="C36" t="n">
         <v>64.34999847412109</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.84514236450195</v>
+        <v>36.84514617919922</v>
       </c>
       <c r="C37" t="n">
         <v>61.81999969482422</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>32.71020889282227</v>
+        <v>32.71022033691406</v>
       </c>
       <c r="C38" t="n">
         <v>54.5</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.91102600097656</v>
+        <v>28.91101455688477</v>
       </c>
       <c r="C39" t="n">
         <v>48.16999816894531</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>28.2628116607666</v>
+        <v>28.26281929016113</v>
       </c>
       <c r="C40" t="n">
         <v>47.09000015258789</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.92961692810059</v>
+        <v>29.92961311340332</v>
       </c>
       <c r="C41" t="n">
         <v>49.43999862670898</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.44304466247559</v>
+        <v>31.44303703308105</v>
       </c>
       <c r="C42" t="n">
         <v>51.93999862670898</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>30.93452453613281</v>
+        <v>30.93453025817871</v>
       </c>
       <c r="C43" t="n">
         <v>51.09999847412109</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>33.87281799316406</v>
+        <v>33.8728141784668</v>
       </c>
       <c r="C44" t="n">
         <v>55.5099983215332</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.01852798461914</v>
+        <v>33.01851272583008</v>
       </c>
       <c r="C45" t="n">
         <v>54.11000061035156</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>35.34341812133789</v>
+        <v>35.34342956542969</v>
       </c>
       <c r="C46" t="n">
         <v>57.91999816894531</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>35.66217422485352</v>
+        <v>35.66218185424805</v>
       </c>
       <c r="C47" t="n">
         <v>58</v>
@@ -1403,7 +1403,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>37.27926254272461</v>
+        <v>37.27927398681641</v>
       </c>
       <c r="C49" t="n">
         <v>60.63000106811523</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>38.1166877746582</v>
+        <v>38.11667251586914</v>
       </c>
       <c r="C50" t="n">
         <v>61.54999923706055</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>39.18803405761719</v>
+        <v>39.18804168701172</v>
       </c>
       <c r="C51" t="n">
         <v>63.27999877929688</v>
@@ -1478,7 +1478,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.18182373046875</v>
+        <v>39.18183517456055</v>
       </c>
       <c r="C52" t="n">
         <v>63.27000045776367</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.79070281982422</v>
+        <v>38.79068756103516</v>
       </c>
       <c r="C53" t="n">
         <v>62.15999984741211</v>
@@ -1528,7 +1528,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>38.12298202514648</v>
+        <v>38.12297058105469</v>
       </c>
       <c r="C54" t="n">
         <v>61.09000015258789</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.43027877807617</v>
+        <v>37.4302864074707</v>
       </c>
       <c r="C55" t="n">
         <v>59.97999954223633</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.46535873413086</v>
+        <v>38.46536254882812</v>
       </c>
       <c r="C56" t="n">
         <v>61.15999984741211</v>
@@ -1632,7 +1632,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>37.7169303894043</v>
+        <v>37.71694183349609</v>
       </c>
       <c r="C58" t="n">
         <v>59.97000122070312</v>
@@ -1661,7 +1661,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.28843307495117</v>
+        <v>40.28842544555664</v>
       </c>
       <c r="C59" t="n">
         <v>63.56999969482422</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>38.70401763916016</v>
+        <v>38.70401000976562</v>
       </c>
       <c r="C60" t="n">
         <v>61.06999969482422</v>
@@ -1719,7 +1719,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.77009582519531</v>
+        <v>40.77010726928711</v>
       </c>
       <c r="C61" t="n">
         <v>64.33000183105469</v>
@@ -1748,7 +1748,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>40.30619430541992</v>
+        <v>40.3061637878418</v>
       </c>
       <c r="C62" t="n">
         <v>63.13000106811523</v>
@@ -1777,7 +1777,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>40.2551155090332</v>
+        <v>40.25512313842773</v>
       </c>
       <c r="C63" t="n">
         <v>63.04999923706055</v>
@@ -1806,7 +1806,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>39.3293342590332</v>
+        <v>39.32933807373047</v>
       </c>
       <c r="C64" t="n">
         <v>61.59999847412109</v>
@@ -1864,7 +1864,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.13178634643555</v>
+        <v>43.13179016113281</v>
       </c>
       <c r="C66" t="n">
         <v>67</v>
@@ -1893,7 +1893,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>40.92370223999023</v>
+        <v>40.92369842529297</v>
       </c>
       <c r="C67" t="n">
         <v>63.56999969482422</v>
@@ -1922,7 +1922,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.90896987915039</v>
+        <v>39.90897369384766</v>
       </c>
       <c r="C68" t="n">
         <v>61.4900016784668</v>
@@ -1951,7 +1951,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>41.33035659790039</v>
+        <v>41.33036041259766</v>
       </c>
       <c r="C69" t="n">
         <v>63.68000030517578</v>
@@ -1980,7 +1980,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>41.00583267211914</v>
+        <v>41.00582885742188</v>
       </c>
       <c r="C70" t="n">
         <v>63.18000030517578</v>
@@ -2009,7 +2009,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.87015914916992</v>
+        <v>41.87015151977539</v>
       </c>
       <c r="C71" t="n">
         <v>63.9900016784668</v>
@@ -2038,7 +2038,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>42.24965667724609</v>
+        <v>42.24966049194336</v>
       </c>
       <c r="C72" t="n">
         <v>64.56999969482422</v>
@@ -2067,7 +2067,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.64990234375</v>
+        <v>43.64992523193359</v>
       </c>
       <c r="C73" t="n">
         <v>66.70999908447266</v>
@@ -2096,7 +2096,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.57797622680664</v>
+        <v>41.57799530029297</v>
       </c>
       <c r="C74" t="n">
         <v>63.04000091552734</v>
@@ -2125,7 +2125,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>44.59872055053711</v>
+        <v>44.59872436523438</v>
       </c>
       <c r="C75" t="n">
         <v>67.62000274658203</v>
@@ -2154,7 +2154,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>44.32830047607422</v>
+        <v>44.32831573486328</v>
       </c>
       <c r="C76" t="n">
         <v>67.20999908447266</v>
@@ -2183,7 +2183,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>42.32876968383789</v>
+        <v>42.32878112792969</v>
       </c>
       <c r="C77" t="n">
         <v>63.63999938964844</v>
@@ -2212,7 +2212,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>41.43083953857422</v>
+        <v>41.43084335327148</v>
       </c>
       <c r="C78" t="n">
         <v>62.29000091552734</v>
@@ -2241,7 +2241,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>40.73910140991211</v>
+        <v>40.73909378051758</v>
       </c>
       <c r="C79" t="n">
         <v>61.25</v>
@@ -2270,7 +2270,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>43.29974365234375</v>
+        <v>43.29974746704102</v>
       </c>
       <c r="C80" t="n">
         <v>64.54000091552734</v>
@@ -2299,7 +2299,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>45.07762145996094</v>
+        <v>45.07762908935547</v>
       </c>
       <c r="C81" t="n">
         <v>67.19000244140625</v>
@@ -2328,7 +2328,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>46.53348159790039</v>
+        <v>46.53347015380859</v>
       </c>
       <c r="C82" t="n">
         <v>69.36000061035156</v>
@@ -2444,7 +2444,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>51.25094223022461</v>
+        <v>51.25093841552734</v>
       </c>
       <c r="C86" t="n">
         <v>75.16000366210938</v>
@@ -2473,7 +2473,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>51.94646835327148</v>
+        <v>51.94647598266602</v>
       </c>
       <c r="C87" t="n">
         <v>76.18000030517578</v>
@@ -2502,7 +2502,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.54655075073242</v>
+        <v>52.54653549194336</v>
       </c>
       <c r="C88" t="n">
         <v>77.05999755859375</v>
@@ -2531,7 +2531,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.73340225219727</v>
+        <v>52.73340606689453</v>
       </c>
       <c r="C89" t="n">
         <v>76.76999664306641</v>
@@ -2560,7 +2560,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>52.72652053833008</v>
+        <v>52.72653579711914</v>
       </c>
       <c r="C90" t="n">
         <v>76.76000213623047</v>
@@ -2589,7 +2589,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>52.88451385498047</v>
+        <v>52.88450622558594</v>
       </c>
       <c r="C91" t="n">
         <v>76.98999786376953</v>
@@ -2618,7 +2618,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.57132720947266</v>
+        <v>55.57130432128906</v>
       </c>
       <c r="C92" t="n">
         <v>80.30000305175781</v>
@@ -2647,7 +2647,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.90349197387695</v>
+        <v>53.90349578857422</v>
       </c>
       <c r="C93" t="n">
         <v>77.88999938964844</v>
@@ -2676,7 +2676,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>52.3117790222168</v>
+        <v>52.31179809570312</v>
       </c>
       <c r="C94" t="n">
         <v>75.58999633789062</v>
@@ -2705,7 +2705,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>56.31965637207031</v>
+        <v>56.31966781616211</v>
       </c>
       <c r="C95" t="n">
         <v>80.75</v>
@@ -2734,7 +2734,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>58.73982620239258</v>
+        <v>58.73983764648438</v>
       </c>
       <c r="C96" t="n">
         <v>84.22000122070312</v>
@@ -2763,7 +2763,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.77997207641602</v>
+        <v>56.77996444702148</v>
       </c>
       <c r="C97" t="n">
         <v>81.41000366210938</v>
@@ -2792,7 +2792,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>53.84341812133789</v>
+        <v>53.84341049194336</v>
       </c>
       <c r="C98" t="n">
         <v>76.62000274658203</v>
@@ -2821,7 +2821,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.27700042724609</v>
+        <v>55.27698516845703</v>
       </c>
       <c r="C99" t="n">
         <v>78.66000366210938</v>
@@ -2850,7 +2850,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.64030838012695</v>
+        <v>56.6402702331543</v>
       </c>
       <c r="C100" t="n">
         <v>80.59999847412109</v>
@@ -2879,7 +2879,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>58.47409057617188</v>
+        <v>58.47409820556641</v>
       </c>
       <c r="C101" t="n">
         <v>82.55000305175781</v>
@@ -2908,7 +2908,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>57.22739410400391</v>
+        <v>57.22740173339844</v>
       </c>
       <c r="C102" t="n">
         <v>80.79000091552734</v>
@@ -2937,7 +2937,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>55.66904067993164</v>
+        <v>55.66901779174805</v>
       </c>
       <c r="C103" t="n">
         <v>78.58999633789062</v>
@@ -2966,7 +2966,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>55.20697021484375</v>
+        <v>55.20696258544922</v>
       </c>
       <c r="C104" t="n">
         <v>77.31999969482422</v>
@@ -2995,7 +2995,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>59.34105682373047</v>
+        <v>59.34109115600586</v>
       </c>
       <c r="C105" t="n">
         <v>83.11000061035156</v>
@@ -3082,7 +3082,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.06279754638672</v>
+        <v>65.06281280517578</v>
       </c>
       <c r="C108" t="n">
         <v>90.43000030517578</v>
@@ -3111,7 +3111,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.53765106201172</v>
+        <v>65.53765869140625</v>
       </c>
       <c r="C109" t="n">
         <v>91.08999633789062</v>
@@ -3140,7 +3140,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>61.07651138305664</v>
+        <v>61.07653045654297</v>
       </c>
       <c r="C110" t="n">
         <v>84.29000091552734</v>
@@ -3169,7 +3169,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>61.6851921081543</v>
+        <v>61.68520355224609</v>
       </c>
       <c r="C111" t="n">
         <v>85.12999725341797</v>
@@ -3198,7 +3198,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>59.37370681762695</v>
+        <v>59.37370300292969</v>
       </c>
       <c r="C112" t="n">
         <v>81.94000244140625</v>
@@ -3227,7 +3227,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>58.07633209228516</v>
+        <v>58.07633590698242</v>
       </c>
       <c r="C113" t="n">
         <v>79.51000213623047</v>
@@ -3256,7 +3256,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>57.25827407836914</v>
+        <v>57.25825119018555</v>
       </c>
       <c r="C114" t="n">
         <v>78.38999938964844</v>
@@ -3314,7 +3314,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>56.48258972167969</v>
+        <v>56.48258209228516</v>
       </c>
       <c r="C116" t="n">
         <v>76.69999694824219</v>
@@ -3343,7 +3343,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>52.04204559326172</v>
+        <v>52.04204940795898</v>
       </c>
       <c r="C117" t="n">
         <v>70.66999816894531</v>
@@ -3372,7 +3372,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>52.97727584838867</v>
+        <v>52.97729110717773</v>
       </c>
       <c r="C118" t="n">
         <v>71.94000244140625</v>
@@ -3401,7 +3401,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.75244903564453</v>
+        <v>56.75246429443359</v>
       </c>
       <c r="C119" t="n">
         <v>76.37999725341797</v>
@@ -3430,7 +3430,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>55.60819625854492</v>
+        <v>55.60821533203125</v>
       </c>
       <c r="C120" t="n">
         <v>74.83999633789062</v>
@@ -3488,7 +3488,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>61.22701644897461</v>
+        <v>61.22699356079102</v>
       </c>
       <c r="C122" t="n">
         <v>81.69000244140625</v>
@@ -3517,7 +3517,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.17765808105469</v>
+        <v>60.17768859863281</v>
       </c>
       <c r="C123" t="n">
         <v>80.29000091552734</v>
@@ -3546,7 +3546,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>61.69167709350586</v>
+        <v>61.69166946411133</v>
       </c>
       <c r="C124" t="n">
         <v>82.30999755859375</v>
@@ -3575,7 +3575,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.54217910766602</v>
+        <v>60.54219055175781</v>
       </c>
       <c r="C125" t="n">
         <v>80.12000274658203</v>
@@ -3604,7 +3604,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>61.23736953735352</v>
+        <v>61.23736572265625</v>
       </c>
       <c r="C126" t="n">
         <v>81.04000091552734</v>
@@ -3633,7 +3633,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>63.9803466796875</v>
+        <v>63.9803581237793</v>
       </c>
       <c r="C127" t="n">
         <v>84.66999816894531</v>
@@ -3662,7 +3662,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>65.18236541748047</v>
+        <v>65.18235778808594</v>
       </c>
       <c r="C128" t="n">
         <v>85.58999633789062</v>
@@ -3691,7 +3691,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>66.49225616455078</v>
+        <v>66.49227905273438</v>
       </c>
       <c r="C129" t="n">
         <v>87.30999755859375</v>
@@ -3720,7 +3720,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>68.35047149658203</v>
+        <v>68.35048675537109</v>
       </c>
       <c r="C130" t="n">
         <v>89.75</v>
@@ -3749,7 +3749,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>66.61420440673828</v>
+        <v>66.61423492431641</v>
       </c>
       <c r="C131" t="n">
         <v>86.80000305175781</v>
@@ -3778,7 +3778,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.28351211547852</v>
+        <v>63.28349304199219</v>
       </c>
       <c r="C132" t="n">
         <v>82.45999908447266</v>
@@ -3807,7 +3807,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>64.52677917480469</v>
+        <v>64.52677154541016</v>
       </c>
       <c r="C133" t="n">
         <v>84.08000183105469</v>
@@ -3836,7 +3836,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.76095581054688</v>
+        <v>67.76097106933594</v>
       </c>
       <c r="C134" t="n">
         <v>87.59999847412109</v>
@@ -3865,7 +3865,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.44512939453125</v>
+        <v>70.44510650634766</v>
       </c>
       <c r="C135" t="n">
         <v>91.06999969482422</v>
@@ -3894,7 +3894,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>69.50144195556641</v>
+        <v>69.50140380859375</v>
       </c>
       <c r="C136" t="n">
         <v>89.84999847412109</v>
@@ -3923,7 +3923,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.06940460205078</v>
+        <v>68.06941223144531</v>
       </c>
       <c r="C137" t="n">
         <v>87.33000183105469</v>
@@ -4097,7 +4097,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>68.33396148681641</v>
+        <v>68.33397674560547</v>
       </c>
       <c r="C143" t="n">
         <v>86.33999633789062</v>
@@ -4126,7 +4126,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>71.22277069091797</v>
+        <v>71.22275543212891</v>
       </c>
       <c r="C144" t="n">
         <v>89.98999786376953</v>
@@ -4155,7 +4155,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>72.71862030029297</v>
+        <v>72.71861267089844</v>
       </c>
       <c r="C145" t="n">
         <v>91.87999725341797</v>
@@ -4184,7 +4184,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>68.85491943359375</v>
+        <v>68.85488891601562</v>
       </c>
       <c r="C146" t="n">
         <v>86.33999633789062</v>
@@ -4213,7 +4213,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>62.61856842041016</v>
+        <v>62.61856079101562</v>
       </c>
       <c r="C147" t="n">
         <v>78.51999664306641</v>
@@ -4242,7 +4242,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>63.22466278076172</v>
+        <v>63.22465133666992</v>
       </c>
       <c r="C148" t="n">
         <v>79.27999877929688</v>
@@ -4271,7 +4271,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>58.22395324707031</v>
+        <v>58.22396087646484</v>
       </c>
       <c r="C149" t="n">
         <v>72.33999633789062</v>
@@ -4300,7 +4300,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>58.89199447631836</v>
+        <v>58.89199066162109</v>
       </c>
       <c r="C150" t="n">
         <v>73.16999816894531</v>
@@ -4329,7 +4329,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>62.82777404785156</v>
+        <v>62.82779693603516</v>
       </c>
       <c r="C151" t="n">
         <v>78.05999755859375</v>
@@ -4358,7 +4358,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>65.68832397460938</v>
+        <v>65.68830871582031</v>
       </c>
       <c r="C152" t="n">
         <v>80.87999725341797</v>
@@ -4387,7 +4387,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>67.3695068359375</v>
+        <v>67.36948394775391</v>
       </c>
       <c r="C153" t="n">
         <v>82.94999694824219</v>
@@ -4445,7 +4445,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>72.65962982177734</v>
+        <v>72.65964508056641</v>
       </c>
       <c r="C155" t="n">
         <v>88.68000030517578</v>
@@ -4503,7 +4503,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>75.31432342529297</v>
+        <v>75.31433868408203</v>
       </c>
       <c r="C157" t="n">
         <v>91.91999816894531</v>
@@ -4532,7 +4532,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>79.66751098632812</v>
+        <v>79.66753387451172</v>
       </c>
       <c r="C158" t="n">
         <v>96.47000122070312</v>
@@ -4590,7 +4590,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>85.92730712890625</v>
+        <v>85.92729949951172</v>
       </c>
       <c r="C160" t="n">
         <v>104.0500030517578</v>
@@ -4619,7 +4619,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>88.55482482910156</v>
+        <v>88.55481719970703</v>
       </c>
       <c r="C161" t="n">
         <v>106.4800033569336</v>
@@ -4648,7 +4648,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>85.58579254150391</v>
+        <v>85.58580017089844</v>
       </c>
       <c r="C162" t="n">
         <v>102.9100036621094</v>
@@ -4677,7 +4677,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>91.19117736816406</v>
+        <v>91.19116973876953</v>
       </c>
       <c r="C163" t="n">
         <v>109.6500015258789</v>
@@ -4735,7 +4735,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>100.6376190185547</v>
+        <v>100.6376342773438</v>
       </c>
       <c r="C165" t="n">
         <v>120.2300033569336</v>
@@ -4793,7 +4793,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>104.8859329223633</v>
+        <v>104.8859252929688</v>
       </c>
       <c r="C167" t="n">
         <v>124.5100021362305</v>
@@ -4822,7 +4822,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>102.8220672607422</v>
+        <v>102.8220596313477</v>
       </c>
       <c r="C168" t="n">
         <v>122.0599975585938</v>
@@ -4851,7 +4851,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>105.2144317626953</v>
+        <v>105.2144546508789</v>
       </c>
       <c r="C169" t="n">
         <v>124.9000015258789</v>
@@ -4880,7 +4880,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>105.6022796630859</v>
+        <v>105.6023025512695</v>
       </c>
       <c r="C170" t="n">
         <v>124.620002746582</v>
@@ -4909,7 +4909,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>95.95047760009766</v>
+        <v>95.95048522949219</v>
       </c>
       <c r="C171" t="n">
         <v>113.2300033569336</v>
@@ -4938,7 +4938,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>93.21337890625</v>
+        <v>93.21338653564453</v>
       </c>
       <c r="C172" t="n">
         <v>110</v>
@@ -4967,7 +4967,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>100.5485076904297</v>
+        <v>100.5485153198242</v>
       </c>
       <c r="C173" t="n">
         <v>117.870002746582</v>
@@ -4996,7 +4996,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>98.88504791259766</v>
+        <v>98.88507080078125</v>
       </c>
       <c r="C174" t="n">
         <v>115.9199981689453</v>
@@ -5025,7 +5025,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>101.998664855957</v>
+        <v>101.9986724853516</v>
       </c>
       <c r="C175" t="n">
         <v>119.5699996948242</v>
@@ -5054,7 +5054,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>112.5571594238281</v>
+        <v>112.5571746826172</v>
       </c>
       <c r="C176" t="n">
         <v>131.1199951171875</v>
@@ -5083,7 +5083,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>118.7464218139648</v>
+        <v>118.7464599609375</v>
       </c>
       <c r="C177" t="n">
         <v>138.3300018310547</v>
@@ -5112,7 +5112,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>119.31298828125</v>
+        <v>119.3130264282227</v>
       </c>
       <c r="C178" t="n">
         <v>138.9900054931641</v>
@@ -5141,7 +5141,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>118.3440475463867</v>
+        <v>118.3440628051758</v>
       </c>
       <c r="C179" t="n">
         <v>137.1000061035156</v>
@@ -5170,7 +5170,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>119.8719024658203</v>
+        <v>119.8718948364258</v>
       </c>
       <c r="C180" t="n">
         <v>138.8699951171875</v>
@@ -5228,7 +5228,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>111.3377838134766</v>
+        <v>111.3377990722656</v>
       </c>
       <c r="C182" t="n">
         <v>128.2100067138672</v>
@@ -5257,7 +5257,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>107.273681640625</v>
+        <v>107.2736663818359</v>
       </c>
       <c r="C183" t="n">
         <v>123.5299987792969</v>
@@ -5286,7 +5286,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>117.6076583862305</v>
+        <v>117.6076354980469</v>
       </c>
       <c r="C184" t="n">
         <v>135.4299926757812</v>
@@ -5315,7 +5315,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>116.6034469604492</v>
+        <v>116.6034545898438</v>
       </c>
       <c r="C185" t="n">
         <v>133.4199981689453</v>
@@ -5344,7 +5344,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>117.8532180786133</v>
+        <v>117.8532104492188</v>
       </c>
       <c r="C186" t="n">
         <v>134.8500061035156</v>
@@ -5373,7 +5373,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>117.9231262207031</v>
+        <v>117.9231185913086</v>
       </c>
       <c r="C187" t="n">
         <v>134.9299926757812</v>
@@ -5402,7 +5402,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>125.0847702026367</v>
+        <v>125.0847625732422</v>
       </c>
       <c r="C188" t="n">
         <v>142.2299957275391</v>
@@ -5431,7 +5431,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>125.2254867553711</v>
+        <v>125.2255096435547</v>
       </c>
       <c r="C189" t="n">
         <v>142.3899993896484</v>
@@ -5460,7 +5460,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>122.9477310180664</v>
+        <v>122.9477233886719</v>
       </c>
       <c r="C190" t="n">
         <v>139.8000030517578</v>
@@ -5489,7 +5489,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>126.5327529907227</v>
+        <v>126.5327377319336</v>
       </c>
       <c r="C191" t="n">
         <v>142.9900054931641</v>
@@ -5547,7 +5547,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>144.7529602050781</v>
+        <v>144.7529907226562</v>
       </c>
       <c r="C193" t="n">
         <v>163.5800018310547</v>
@@ -5576,7 +5576,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>142.7498168945312</v>
+        <v>142.7498626708984</v>
       </c>
       <c r="C194" t="n">
         <v>160.4499969482422</v>
@@ -5605,7 +5605,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>138.6929168701172</v>
+        <v>138.6928405761719</v>
       </c>
       <c r="C195" t="n">
         <v>155.8899993896484</v>
@@ -5634,7 +5634,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>135.9437713623047</v>
+        <v>135.9437255859375</v>
       </c>
       <c r="C196" t="n">
         <v>152.8000030517578</v>
@@ -5663,7 +5663,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>143.6401519775391</v>
+        <v>143.6401672363281</v>
       </c>
       <c r="C197" t="n">
         <v>160.5500030517578</v>
@@ -5692,7 +5692,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>132.3046264648438</v>
+        <v>132.3046417236328</v>
       </c>
       <c r="C198" t="n">
         <v>147.8800048828125</v>
@@ -5721,7 +5721,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>128.6454315185547</v>
+        <v>128.6454010009766</v>
       </c>
       <c r="C199" t="n">
         <v>143.7899932861328</v>
@@ -5779,7 +5779,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>124.2127227783203</v>
+        <v>124.2127151489258</v>
       </c>
       <c r="C201" t="n">
         <v>137.9400024414062</v>
@@ -5808,7 +5808,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>113.6860733032227</v>
+        <v>113.6860809326172</v>
       </c>
       <c r="C202" t="n">
         <v>126.25</v>
@@ -5837,7 +5837,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>122.128776550293</v>
+        <v>122.1287689208984</v>
       </c>
       <c r="C203" t="n">
         <v>134.6699981689453</v>
@@ -5924,7 +5924,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>129.9310150146484</v>
+        <v>129.9309997558594</v>
       </c>
       <c r="C206" t="n">
         <v>142.3800048828125</v>
@@ -5953,7 +5953,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>125.532470703125</v>
+        <v>125.5324401855469</v>
       </c>
       <c r="C207" t="n">
         <v>137.5599975585938</v>
@@ -6011,7 +6011,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>143.6004180908203</v>
+        <v>143.6003875732422</v>
       </c>
       <c r="C209" t="n">
         <v>156.3800048828125</v>
@@ -6040,7 +6040,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>130.8546905517578</v>
+        <v>130.8546752929688</v>
       </c>
       <c r="C210" t="n">
         <v>142.5</v>
@@ -6069,7 +6069,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>139.339599609375</v>
+        <v>139.3396148681641</v>
       </c>
       <c r="C211" t="n">
         <v>151.7400054931641</v>
@@ -6127,7 +6127,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.6200866699219</v>
+        <v>142.6201019287109</v>
       </c>
       <c r="C213" t="n">
         <v>154.3399963378906</v>
@@ -6156,7 +6156,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>134.7839965820312</v>
+        <v>134.7840270996094</v>
       </c>
       <c r="C214" t="n">
         <v>145.8600006103516</v>
@@ -6214,7 +6214,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>142.7577514648438</v>
+        <v>142.7577362060547</v>
       </c>
       <c r="C216" t="n">
         <v>153.5200042724609</v>
@@ -6272,7 +6272,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>147.0468139648438</v>
+        <v>147.0467987060547</v>
       </c>
       <c r="C218" t="n">
         <v>157.1399993896484</v>
@@ -6301,7 +6301,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>148.731201171875</v>
+        <v>148.7311859130859</v>
       </c>
       <c r="C219" t="n">
         <v>158.9400024414062</v>
@@ -6359,7 +6359,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>153.7037048339844</v>
+        <v>153.7036590576172</v>
       </c>
       <c r="C221" t="n">
         <v>163.1999969482422</v>
@@ -6417,7 +6417,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>155.3235778808594</v>
+        <v>155.3236083984375</v>
       </c>
       <c r="C223" t="n">
         <v>164.9199981689453</v>
@@ -6446,7 +6446,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>152.3162384033203</v>
+        <v>152.3162536621094</v>
       </c>
       <c r="C224" t="n">
         <v>160.7599945068359</v>
@@ -6504,7 +6504,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>164.1028900146484</v>
+        <v>164.1028747558594</v>
       </c>
       <c r="C226" t="n">
         <v>173.1999969482422</v>
@@ -6533,7 +6533,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>157.4242858886719</v>
+        <v>157.4242706298828</v>
       </c>
       <c r="C227" t="n">
         <v>165.1799926757812</v>
@@ -6562,7 +6562,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>170.8431854248047</v>
+        <v>170.8431701660156</v>
       </c>
       <c r="C228" t="n">
         <v>179.2599945068359</v>
@@ -6620,7 +6620,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>159.1609191894531</v>
+        <v>159.160888671875</v>
       </c>
       <c r="C230" t="n">
         <v>165.9900054931641</v>
@@ -6678,7 +6678,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>163.4086303710938</v>
+        <v>163.4086151123047</v>
       </c>
       <c r="C232" t="n">
         <v>170.4199981689453</v>
@@ -6707,7 +6707,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>156.8532562255859</v>
+        <v>156.853271484375</v>
       </c>
       <c r="C233" t="n">
         <v>162.5700073242188</v>
@@ -6736,7 +6736,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>163.9158630371094</v>
+        <v>163.9158477783203</v>
       </c>
       <c r="C234" t="n">
         <v>169.8899993896484</v>
@@ -6852,7 +6852,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>149.2607269287109</v>
+        <v>149.2607116699219</v>
       </c>
       <c r="C238" t="n">
         <v>153.6499938964844</v>
@@ -6881,7 +6881,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>147.0959167480469</v>
+        <v>147.0959014892578</v>
       </c>
       <c r="C239" t="n">
         <v>150.3699951171875</v>
